--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Remote Azure Cloud Engineer</t>
+          <t>AI Applications Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Regional Physicians</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17f6626567905dd</t>
+          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Silver Opportunity Partners LLC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kellogg, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Remote Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
+          <t>https://www.indeed.com/viewjob?jk=e17f6626567905dd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Silver Opportunity Partners LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Kellogg, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>EBSCO Information Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=37294b654b8dfdfa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior ML Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f1aa8551c5f292</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior ML Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=05f1aa8551c5f292</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Software Engineer</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824480af2e1c826c</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Metrics Engineer - Grafana</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f968d07ba6cb70f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer - Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=824480af2e1c826c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=62cf7aec7b000416</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Senior Metrics Engineer - Grafana</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=f968d07ba6cb70f4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>SCP Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=aae33a9a018f9fb8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,367 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BI Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Health Care Service Corporation</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UVA Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>University of Virginia</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI DevOps / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hermeus</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mission Produce</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Oxnard, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Remote Azure Cloud Engineer</t>
+          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Silver Opportunity Partners LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Kellogg, ID, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17f6626567905dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silver Opportunity Partners LLC</t>
+          <t>EBSCO Information Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kellogg, ID, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,52 +976,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>AssetWorks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=6de4a61bfe7bafa4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,15 +3111,85 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mission Produce</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Oxnard, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silver Opportunity Partners LLC</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kellogg, ID, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>Silver Opportunity Partners LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Kellogg, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
+          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
         </is>
       </c>
     </row>
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>EBSCO Information Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,52 +976,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AssetWorks</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de4a61bfe7bafa4</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>AssetWorks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6de4a61bfe7bafa4</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ITRIKA INC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37294b654b8dfdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=37294b654b8dfdfa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Kong API Developer / API Gateway Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>LVTLABS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hawthorn Wds, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=26b193a0ca9b282b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior ML Engineer II</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f1aa8551c5f292</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Architect | Fort Worth, TX (Sponsorship not provided)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TTI, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b27ee1ed5c38b053</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior ML Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=05f1aa8551c5f292</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Software Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824480af2e1c826c</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cf7aec7b000416</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Metrics Engineer - Grafana</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f968d07ba6cb70f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer - Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=824480af2e1c826c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=62cf7aec7b000416</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Senior Metrics Engineer - Grafana</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=f968d07ba6cb70f4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SCP Health</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aae33a9a018f9fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Intent Design Pvt Ltd</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=753eee17cd52656e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Senior Service Reliability Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,164 +2806,164 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>SCP Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+          <t>https://www.indeed.com/viewjob?jk=aae33a9a018f9fb8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,29 +2971,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,400 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UVA Health</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>University of Virginia</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Capp</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FocusKPI Inc.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mission Produce</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oxnard, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silver Opportunity Partners LLC</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kellogg, ID, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,52 +976,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AssetWorks</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de4a61bfe7bafa4</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,77 +1431,77 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37294b654b8dfdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kong API Developer / API Gateway Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LVTLABS</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hawthorn Wds, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b193a0ca9b282b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Fisher's Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Data Scientist, Marketing Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=710a55c7263d5b09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect | Fort Worth, TX (Sponsorship not provided)</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TTI, Inc.</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,112 +1861,112 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27ee1ed5c38b053</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior ML Engineer II</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f1aa8551c5f292</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824480af2e1c826c</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cf7aec7b000416</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Metrics Engineer - Grafana</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f968d07ba6cb70f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intent Design Pvt Ltd</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753eee17cd52656e</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Service Reliability Engineer</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,159 +2806,159 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SCP Health</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer II- Front end/DevOps</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aae33a9a018f9fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,367 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Data Engineer- Microsoft Fabric</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>University of Virginia</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Charlottesville, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Capp</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Network Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>FocusKPI Inc.</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Empower Pharmacy</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>AI/Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Mission Produce</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Oxnard, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,104 +976,104 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ITRIKA INC</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>ITRIKA INC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,104 +1431,104 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fisher's Technology</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Marketing Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710a55c7263d5b09</t>
+          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fisher's Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,94 +1861,94 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II- Front end/DevOps</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Software Engineer II- Front end/DevOps</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,157 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,52 +1011,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>ITRIKA INC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ITRIKA INC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,52 +1466,52 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
+          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fisher's Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
+          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fisher's Technology</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,42 +1896,42 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Engineer II- Front end/DevOps</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II- Front end/DevOps</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Database Engineer - Professional Archive Search</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Hive, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,77 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+          <t>https://www.indeed.com/viewjob?jk=607072382f0dc730</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Silver Opportunity Partners LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Kellogg, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>EBSCO Information Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,104 +1011,104 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ITRIKA INC</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ITRIKA INC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,112 +1466,112 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=37294b654b8dfdfa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fisher's Technology</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Senior Data Architect | Fort Worth, TX (Sponsorship not provided)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>TTI, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=b27ee1ed5c38b053</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fisher's Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,94 +1966,94 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,172 +2351,172 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Security Engineer - Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=1dcfbc446b17e32b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Security Engineer - Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
+          <t>https://www.indeed.com/viewjob?jk=824480af2e1c826c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Solutions Developer for the Office of HPD TECH</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>New York City Department of Housing Preservation &amp; Development</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=edc48c4da4e29c49</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>IT - Developer II - IV (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Cincinnati Insurance Companies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=fc05454b399f43cb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,129 +2841,129 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II- Front end/DevOps</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
+          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
+          <t>https://www.indeed.com/viewjob?jk=aae33a9a018f9fb8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Software Engineer II- Front end/DevOps</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Database Engineer - Professional Archive Search</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,365 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Capp</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FocusKPI Inc.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mission Produce</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oxnard, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Database Engineer - Professional Archive Search</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Hive, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Git, Datadog</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=607072382f0dc730</t>
         </is>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>AI Applications Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texas Regional Physicians</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6436f900bda01324</t>
+          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14776783056c9570</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Applications Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Texas Regional Physicians</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics F&amp;O Architect – Mining</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silver Opportunity Partners LLC</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kellogg, ID, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,172 +776,172 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7233db1f59ca63c</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,137 +1021,137 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ITRIKA INC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ITRIKA INC</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,116 +1567,116 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, RDS, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37294b654b8dfdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,137 +1686,137 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Kafka, SQL Server, dbt</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4810bc0b521803bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,137 +1861,137 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Architect | Fort Worth, TX (Sponsorship not provided)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TTI, Inc.</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27ee1ed5c38b053</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fisher's Technology</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Star Schema, Dimension Tables</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95ced54585e0bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>DMV IT Service LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae570e570d074aa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,89 +2351,89 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Software Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dcfbc446b17e32b</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824480af2e1c826c</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Developer for the Office of HPD TECH</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New York City Department of Housing Preservation &amp; Development</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,81 +2442,81 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc48c4da4e29c49</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT - Developer II - IV (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Cincinnati Insurance Companies</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc05454b399f43cb</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,84 +2666,84 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,15 +2753,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,137 +2771,137 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,742 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Daxko</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aae33a9a018f9fb8</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technical Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Codoxo</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>DoubleVerify</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>DoubleVerify</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>WEX Inc.</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Tiger Analytics</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>PowerBI Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Contingent Crew, LLC</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Core &amp; Main</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Software Engineer II- Front end/DevOps</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b3be2ba2f955b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Capp</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Network Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>FocusKPI Inc.</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>AI/Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Mission Produce</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Oxnard, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Empower Pharmacy</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Database Engineer - Professional Archive Search</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Smarsh</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Hive, Scala, Kafka, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=607072382f0dc730</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,130 +538,130 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Hive, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a759ca089bff0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=bc44924f0b95abaf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Applications Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Texas Regional Physicians</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=31b06bf0600541ad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Applications Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texas Regional Physicians</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Premier Truck Rental</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb26698105fda83</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,112 +766,112 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6a0ff1e37821ea</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e149a4482a17c3cc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ITRIKA INC</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Delta Live Tables, Hadoop, Spark, PySpark, Scala</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b67320ad58483b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,89 +1126,89 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,221 +1217,221 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=c31bc8d5bad8edcc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d416fca036fe4ced</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,322 +1441,322 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=a30cfbf696f3ce41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Presales Solutions Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dremio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Software Engineer (full-stack)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ithaka</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Data Engineer (Gen AI)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cd87f5af20caa9</t>
         </is>
       </c>
     </row>
@@ -1768,195 +1768,195 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=0048890c0db3309f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=db8fe7e60bbd5eec</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=e982505dce1ac7b4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=23cfb9e733715fe0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,54 +2001,54 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,116 +2057,116 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=81cb8276b9830117</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae570e570d074aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1bc568313355d5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,137 +2316,137 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ae682af8576146</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=f834b4ee8d5a00bd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Engineer - React and Python/Node</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Codal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc9aafe56da8514</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Data Enginer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,137 +2456,137 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,252 +2666,4172 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab0f8e743dbbc8d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Avetta</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6cca5213a9a1127</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+          <t>https://www.indeed.com/viewjob?jk=7926e6a4197341bd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>Cloud Infrastructure, Engineer II</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Trinity Logistics</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Seaford, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PandaDoc</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19c145fe1ecd4858</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ISPOT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7112147837b1a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>JENSEN HUGHES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4e1a90130e82ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Back End Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48ffab1d1222b6fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Back End Developer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Back End Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OneMagnify</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PlanOmatic HQ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3aaefba47f7c10dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PlanOmatic HQ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Warren, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Full Stack Developer [US Based Employee]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Vegas Tickets</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Developer II - REMOTE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Michael Baker International</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Integration Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AlayaCare</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ef273d6cf452b9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Integration Developer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AlayaCare</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HealtheConnections</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80b6fb6372627d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DevOps with IoT focus</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Intellimation LLC</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Capp</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RapidSOS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RapidSOS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Medeloop</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3187da15325fa95f</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ISPOT</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96121634d6be16d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Surt AI</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Full- Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9829e6750566d9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Backend Engineer II</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>HackerRank Careers</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7da86ff81783692d</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>BI ETL Data Developer II or III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Miami University</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Oxford, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33ea09264bc221fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Data Platform</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8c4584060d3a513</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Illumio</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DMV IT Service LLC</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Richmond, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Capnexus</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e75674dc09b32a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PropertyPilot</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Manasquan, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Podimetrics, Inc</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BI Engineer I (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NEUMO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Infrastructure</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GoGuardian</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7df0524a9fce0c54</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Graph Databases</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hone health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59f389941a8cc84f</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AI-ML Engineer 1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Universal Avionics Systems Corporation</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tucson, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ISPOT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4ac5e92ec934a8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tebra</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ff32c43e9fb05be</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Software Development Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ALTEN</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=818320f434af5953</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Security Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tebra</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba20b6de4e6a66f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fe418f28e59352b</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Java Application Developer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VerTALENTS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca1ca5deaa6ef924</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Java Application Developer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>VerTALENTS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DevOps Engineer II (CI/CD)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>DevOps Engineer II (CI/CD)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>API Developer Jr.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>MKS2 Technologies</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gametime United</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Intern</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Stream Data Centers</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Application Automation - Summer Intern</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BeyondTrust</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3baf324dcc677e17</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ICT Data Analyst/Scientist</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ICT Data Analyst/Scientist</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b91c9070c3ca5e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Integrated Specialty Coverages</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ecc25eec1bef60d</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5c8b01f19fd6afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Board of Governors of the Federal Reserve System</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>DoubleVerify</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f1b973dfa2ea0a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>DoubleVerify</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DoubleVerify</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Core &amp; Main</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8018d5fd5cf770</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Data Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SimilarWeb</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>FortifyIQ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, MLOps, CI/CD, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50fb60a049e77fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Envoy global</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Envoy global</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SQL Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mechanical Licensing Collective</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Alpaca</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Technical Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Codoxo</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Python Software Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0b909faa3e60ae0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Path Robotics, Inc.</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a265479586368043</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Control Plane</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Aerospike</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c92cd50ce96c5bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Quality Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Circle.so</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Backend</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CaseGuard</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a969f5c65d3bc93</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>FocusKPI Inc.</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Empirx Health</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e30124c2279b172c</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Capp</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Mission Produce</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Oxnard, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
           <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D180" t="n">
         <v>10.4</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>Redhorse Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b06bf0600541ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Premier Truck Rental</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb26698105fda83</t>
+          <t>https://www.indeed.com/viewjob?jk=598c409a60c42c43</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6a0ff1e37821ea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=e149a4482a17c3cc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=952b93720525db5b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6a0ff1e37821ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e149a4482a17c3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31bc8d5bad8edcc</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d416fca036fe4ced</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Presales Solutions Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Dremio</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (full-stack)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Ithaka</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30cfbf696f3ce41</t>
+          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Presales Solutions Architect</t>
+          <t>Data Scientist/ HR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dremio</t>
+          <t>Laurate LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
+          <t>RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b507a68fea2f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (full-stack)</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,52 +1641,52 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a30cfbf696f3ce41</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer (Gen AI)</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cd87f5af20caa9</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0048890c0db3309f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ServiceNow Architect-CTA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Kobe Solutions LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=890b357933d3a41e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8fe7e60bbd5eec</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e982505dce1ac7b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cfb9e733715fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,164 +2001,164 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cb8276b9830117</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,147 +2166,147 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1bc568313355d5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,234 +2316,234 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ae682af8576146</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f834b4ee8d5a00bd</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - React and Python/Node</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Codal</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc9aafe56da8514</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Enginer</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f50316b9208a167</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=12afa7e8f02cc093</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=78361db76661d0d1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab0f8e743dbbc8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Avetta</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, dbt</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6cca5213a9a1127</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
@@ -2853,265 +2853,265 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7926e6a4197341bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c145fe1ecd4858</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7112147837b1a63</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1a90130e82ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ffab1d1222b6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,304 +3156,304 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aaefba47f7c10dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7ee3a099eaf443</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef273d6cf452b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd172caef34abb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=66351c89c3b928b8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HealtheConnections</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b6fb6372627d03</t>
+          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,137 +3681,137 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>DMV IT Service LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,409 +3821,409 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medeloop</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3187da15325fa95f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96121634d6be16d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Snowflake Data Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Offsoar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
+          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Full- Stack Engineer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9829e6750566d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>VerTALENTS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Automation Engineer (Mid level SDET)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Medrio</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8b1483af03cf54</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da86ff81783692d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ea09264bc221fe</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c4584060d3a513</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75674dc09b32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,182 +4441,182 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df0524a9fce0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Graph Databases</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hone health</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f389941a8cc84f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,19 +4626,19 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ac5e92ec934a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4647,138 +4647,138 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff32c43e9fb05be</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AWS)</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818320f434af5953</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Security Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba20b6de4e6a66f5</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4787,116 +4787,116 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe418f28e59352b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VerTALENTS</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1ca5deaa6ef924</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VerTALENTS</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4927,116 +4927,116 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,252 +5046,252 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Senior Software Engineer, Platform &amp; Product</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3baf324dcc677e17</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c9070c3ca5e22</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
@@ -5303,82 +5303,82 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Engineer</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Integrated Specialty Coverages</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ecc25eec1bef60d</t>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5c8b01f19fd6afd</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,1380 +5456,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1b973dfa2ea0a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>DoubleVerify</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>DoubleVerify</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>WEX Inc.</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Tiger Analytics</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Core &amp; Main</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>EDB</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8018d5fd5cf770</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Data Solution Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>SimilarWeb</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>FortifyIQ</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, MLOps, CI/CD, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50fb60a049e77fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Motional</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Envoy global</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Envoy global</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>SQL Engineer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Mechanical Licensing Collective</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Alpaca</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>jamf</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Technical Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Codoxo</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Python Software Engineer</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Lantern</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b909faa3e60ae0</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Path Robotics, Inc.</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a265479586368043</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Control Plane</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Aerospike</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c92cd50ce96c5bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Senior Quality Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Circle.so</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – Backend</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>CaseGuard</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a969f5c65d3bc93</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>FocusKPI Inc.</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad314dbf5fcf61a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e30124c2279b172c</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Capp</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>AI/Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Mission Produce</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Oxnard, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,54 +741,54 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598c409a60c42c43</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=598c409a60c42c43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6a0ff1e37821ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e149a4482a17c3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, Cassandra, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=952b93720525db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6a0ff1e37821ea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e149a4482a17c3cc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Presales Solutions Architect</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dremio</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (full-stack)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist/ HR</t>
+          <t>Presales Solutions Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Laurate LLC</t>
+          <t>Dremio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b507a68fea2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Engineer (full-stack)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Ithaka</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ServiceNow Architect-CTA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kobe Solutions LLC</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890b357933d3a41e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>ServiceNow Architect-CTA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kobe Solutions LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=890b357933d3a41e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,42 +2001,42 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,87 +2166,87 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12afa7e8f02cc093</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78361db76661d0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=12afa7e8f02cc093</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
+          <t>https://www.indeed.com/viewjob?jk=78361db76661d0d1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,52 +2831,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7ee3a099eaf443</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd172caef34abb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9a4a981492f65f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66351c89c3b928b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
+          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7ee3a099eaf443</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd172caef34abb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=66351c89c3b928b8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Snowflake Data Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Offsoar</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
+          <t>https://www.indeed.com/viewjob?jk=00780166cc82c314</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
+          <t>https://www.indeed.com/viewjob?jk=29ad9f0bf20ac8e8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VerTALENTS</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
+          <t>https://www.indeed.com/viewjob?jk=2d9767d8755f659b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Snowflake Data Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Offsoar</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
+          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
+          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Automation Engineer (Mid level SDET)</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Medrio</t>
+          <t>VerTALENTS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8b1483af03cf54</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,29 +4126,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Automation Engineer (Mid level SDET)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Medrio</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8b1483af03cf54</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,29 +4231,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java - Web Search Team</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,104 +4441,104 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>Software Engineer III - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Product</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,24 +5351,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,15 +5456,155 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Redhorse Corporation</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Redhorse Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Applications Developer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Texas Regional Physicians</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
+          <t>AI Applications Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Texas Regional Physicians</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598c409a60c42c43</t>
+          <t>https://www.indeed.com/viewjob?jk=32602a30e2eae4db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=598c409a60c42c43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,29 +836,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Presales Solutions Architect</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dremio</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Presales Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Dremio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30cfbf696f3ce41</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,69 +1991,69 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
@@ -2218,47 +2218,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=12afa7e8f02cc093</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12afa7e8f02cc093</t>
+          <t>https://www.indeed.com/viewjob?jk=78361db76661d0d1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78361db76661d0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,104 +2796,104 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Systems Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7ee3a099eaf443</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9a4a981492f65f</t>
+          <t>https://www.indeed.com/viewjob?jk=92cd172caef34abb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=66351c89c3b928b8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
+          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7ee3a099eaf443</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd172caef34abb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66351c89c3b928b8</t>
+          <t>https://www.indeed.com/viewjob?jk=20ae2aaa86ff3339</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,59 +3611,59 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DMV IT Service LLC</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Richmond, TX, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e35b16ebbf3788</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Data Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Offsoar</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>VerTALENTS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00780166cc82c314</t>
+          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ad9f0bf20ac8e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9767d8755f659b</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Snowflake Data Developer</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Offsoar</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VerTALENTS</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,29 +4126,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Automation Engineer (Mid level SDET)</t>
+          <t>Software Engineer III - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Medrio</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,349 +4196,349 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8b1483af03cf54</t>
+          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java - Web Search Team</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,29 +4686,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=16179533179bf6b7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a5eee6b5267d17</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Product</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,29 +4931,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5360,251 +5360,6 @@
         </is>
       </c>
       <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a26555a7e1695a9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc44924f0b95abaf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d41dba6e5bbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Redhorse Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc44924f0b95abaf</t>
+          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b41af79b3c9df26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Redhorse Corporation</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4559b3285e613ef1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=815657d7c692a1bd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Applications Developer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas Regional Physicians</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,52 +696,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
+          <t>AI Applications Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Texas Regional Physicians</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598c409a60c42c43</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Software Engineer (full-stack)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Ithaka</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (full-stack)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,29 +1816,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>ServiceNow Architect-CTA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Kobe Solutions LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=890b357933d3a41e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ServiceNow Architect-CTA</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kobe Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890b357933d3a41e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,69 +1956,69 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,29 +2236,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78361db76661d0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,52 +2761,52 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7ee3a099eaf443</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92cd172caef34abb</t>
+          <t>https://www.indeed.com/viewjob?jk=20ae2aaa86ff3339</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66351c89c3b928b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,94 +3471,94 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ae2aaa86ff3339</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Snowflake Data Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Offsoar</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>VerTALENTS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Snowflake Data Developer</t>
+          <t>API Developer Jr.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Offsoar</t>
+          <t>MKS2 Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Data Scientist | Growth</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
+          <t>https://www.indeed.com/viewjob?jk=821c175cd2e0b038</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VerTALENTS</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Software Engineer III - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,174 +4056,174 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java - Web Search Team</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,24 +4266,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Quality Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,29 +4546,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2b2de1091c327b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Product</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16179533179bf6b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a5eee6b5267d17</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Systems Engineer (Tableau Platform)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
+          <t>AWS, Azure, GCP, Scala, Tableau, Tableau Server, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,147 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
+          <t>https://www.indeed.com/viewjob?jk=0f014f9a893bbc2e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-22.xlsx
+++ b/results/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Glacier Analytics LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f2c6e67bc23530</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Redhorse Corporation</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Redhorse Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b41af79b3c9df26</t>
+          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4559b3285e613ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>AWS Architect with AI + Automation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>ERP Initiatives Group Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815657d7c692a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=46058fb33ffd00c5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>AI Applications Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Texas Regional Physicians</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,52 +696,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Applications Developer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Texas Regional Physicians</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507d9cc374179ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
+          <t>Senior Cloud Engineer - Remote US</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, ECS, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,29 +836,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c77dba97763b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
         </is>
       </c>
     </row>
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b240190f37e48e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ee2ebd6b94c60</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6a0ff1e37821ea</t>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Analytics Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e149a4482a17c3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,29 +1186,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b7c50c8b7774c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>CA IAM Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, clustering keys, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,94 +1371,94 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f7dd47c3f8803c</t>
+          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CA IAM Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Snowflake, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8d75516142a508</t>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Databricks, GCP, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,134 +1501,134 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineering</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
+          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Presales Solutions Architect</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dremio</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1637,133 +1637,133 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Hadoop, HDFS, Hive, MapReduce, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cafcc6ca50d5961</t>
+          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (full-stack)</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728e8079e1309fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, Azure, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,11 +1773,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1786,24 +1786,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1812,46 +1812,46 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ServiceNow Architect-CTA</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kobe Solutions LLC</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Event Hubs, Zookeeper, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,172 +1861,172 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890b357933d3a41e</t>
+          <t>https://www.indeed.com/viewjob?jk=66f8131b391d620e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Focus Financial Partners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Software Development Engineer - Credential API</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e09f867e58f64d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,102 +2036,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccbfb275c784c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b67c42af6bdf7f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Contributory Network</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed12a9528f47173</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Python Engineer</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,94 +2141,94 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Focus Financial Partners</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Credential API</t>
+          <t>Senior Data Engineer, Scala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c302fda1f6ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Scala</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, ECS, RDS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44346e5b384cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, AWS CodePipeline, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9663ecc56297d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4c16398c048d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contributory Network</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Spark, Kafka, Snowflake, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Integration Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AlayaCare</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,59 +2446,59 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66613c1418d016b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,15 +2508,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,207 +2526,207 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12afa7e8f02cc093</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db30d95b3c9850f2</t>
+          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b4dc32667584fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4197b722f1b29f84</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,59 +2736,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Integration Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AlayaCare</t>
+          <t>RapidSOS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6930b008143758</t>
+          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f64235fd5c4fac6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Braintree, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Azure, Databricks, Spark, Kafka, Oracle, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0f1071f3e2b14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Trust/Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4254814d062ad92d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903bc43e147b726e</t>
+          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Backend Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666758a830bafe1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,207 +3016,207 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2dccb9477bbad2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>BI Engineer I (Hybrid)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d356cba46c60202</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer, Ads Infra - Serving and Foundation</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
+          <t>https://www.indeed.com/viewjob?jk=e26cb9e516d559dc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>AI-ML Engineer 1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Universal Avionics Systems Corporation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b41c02a0117abfda</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,94 +3296,94 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facf27c6b3631798</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9bb1ef1dd7ba48</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Streamline Healthcare Solutions</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ae2aaa86ff3339</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI-ML Engineer 1</t>
+          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Universal Avionics Systems Corporation</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, Spark, Scala, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Stream Data Centers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1d3fe1d3532916</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Gametime United</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,112 +3496,112 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad79b56c244d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=d561d8c2375dd6b1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BI Engineer I (Hybrid)</t>
+          <t>Senior Infrastructure Engineer-Azure Data &amp; Analytics Engineer - State National</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2a5858f9149296</t>
+          <t>https://www.indeed.com/viewjob?jk=94507e2995b9ee29</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Snowflake Data Developer</t>
+          <t>Data Engineer II - Information Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Offsoar</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Snowflake, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,159 +3611,159 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a561b0e7509b746a</t>
+          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Barstow, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Data Engineer - Seattle, WA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VerTALENTS</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e3b4b0db18ccca</t>
+          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f1b91177c8837</t>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e48ff9fd9e13db3</t>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>API Developer Jr.</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MKS2 Technologies</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3772,103 +3772,103 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1737c64b80db08a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Scientist | Growth</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Envoy global</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow, Python, SQL</t>
+          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821c175cd2e0b038</t>
+          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>SQL Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Mechanical Licensing Collective</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Headspace</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3877,116 +3877,116 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer - DevSecOps (Associate, Experienced or Senior)</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe37944ff3c78ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>University of Maryland Medical System</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Strategist (Data Warehouse &amp; Reporting)</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Stream Data Centers</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,19 +3996,19 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ca2b52928b979f</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gametime United</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4017,46 +4017,46 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java - Web Search Team</t>
+          <t>Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60df58e4983d849c</t>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>University of Maryland Medical System</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer II - Information Technology</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b222160bc0c2b3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Technical Operations Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oxnard, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, NoSQL, ETL, Airflow, Bitbucket, CloudWatch</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
+          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Barstow, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c300d9777dc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer - Seattle, WA</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894fb5b066595659</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Engineer, Developer Platform (Cloud Apps)</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d81e4212199a1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Envoy global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, Splunk, CI/CD, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276b3164ac33893</t>
+          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SQL Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mechanical Licensing Collective</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Scala, Oracle, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db429a534810fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf5cd1df0f54fe6</t>
+          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae2d7c352959fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr Quality Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2b2de1091c327b</t>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f9736f5f852f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,612 +4616,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66c9de7a81a7d66</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Ware Malcomb</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Scala, Kafka, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c08697ee3f4bc0ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Capp</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>AI/Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Mission Produce</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Oxnard, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56afd442294fd678</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=243990c269c56673</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d53f3c6ff20349</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d0312c67f01746</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Metropolis</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, PostgreSQL, MySQL, Airflow, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Hadoop, Hive, Spark, PySpark, Spark Streaming, Kafka, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Systems Engineer (Tableau Platform)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Tableau, Tableau Server, Splunk, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f014f9a893bbc2e</t>
         </is>
       </c>
     </row>
